--- a/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>SILO</t>
   </si>
@@ -1262,8 +1262,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>800</v>
       </c>
       <c r="E17" s="3">
         <v>1100</v>
@@ -1612,8 +1612,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-700</v>
       </c>
       <c r="E23" s="3">
         <v>-1000</v>
@@ -1807,8 +1807,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-700</v>
       </c>
       <c r="E26" s="3">
         <v>-1000</v>
@@ -1872,8 +1872,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-700</v>
       </c>
       <c r="E27" s="3">
         <v>-1000</v>
@@ -2262,8 +2262,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-700</v>
       </c>
       <c r="E33" s="3">
         <v>-1000</v>
@@ -2392,8 +2392,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-700</v>
       </c>
       <c r="E35" s="3">
         <v>-1000</v>
@@ -4932,8 +4932,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-700</v>
       </c>
       <c r="E81" s="3">
         <v>-1000</v>

--- a/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>SILO</t>
   </si>
@@ -656,107 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -820,8 +827,14 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -859,13 +872,13 @@
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
@@ -876,17 +889,23 @@
       <c r="T9" s="3">
         <v>0</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>4</v>
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -924,14 +943,14 @@
         <v>0</v>
       </c>
       <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-100</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
       <c r="R10" s="3">
         <v>0</v>
       </c>
@@ -941,17 +960,23 @@
       <c r="T10" s="3">
         <v>0</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,49 +1000,51 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
       </c>
       <c r="G12" s="3">
+        <v>100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
-        <v>100</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
+        <v>100</v>
+      </c>
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
-        <v>100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
-      </c>
       <c r="N12" s="3">
         <v>100</v>
       </c>
       <c r="O12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
@@ -1026,13 +1053,13 @@
         <v>0</v>
       </c>
       <c r="S12" s="3">
-        <v>100</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>100</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>4</v>
@@ -1040,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1138,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1119,59 +1158,65 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W14" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,8 +1280,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,73 +1308,81 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E17" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="F17" s="3">
         <v>800</v>
       </c>
       <c r="G17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>800</v>
+      </c>
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1000</v>
       </c>
       <c r="L17" s="3">
         <v>500</v>
       </c>
       <c r="M17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>500</v>
+      </c>
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
-      </c>
-      <c r="R17" s="3">
-        <v>200</v>
-      </c>
-      <c r="S17" s="3">
-        <v>400</v>
       </c>
       <c r="T17" s="3">
         <v>200</v>
       </c>
       <c r="U17" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="V17" s="3">
         <v>200</v>
       </c>
       <c r="W17" s="3">
+        <v>200</v>
+      </c>
+      <c r="X17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1331,64 +1390,70 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="F18" s="3">
         <v>-800</v>
       </c>
       <c r="G18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1000</v>
       </c>
       <c r="L18" s="3">
         <v>-500</v>
       </c>
       <c r="M18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-400</v>
       </c>
       <c r="T18" s="3">
         <v>-200</v>
       </c>
       <c r="U18" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="V18" s="3">
         <v>-200</v>
       </c>
       <c r="W18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,8 +1477,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1424,37 +1491,37 @@
         <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
       </c>
       <c r="L20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N20" s="3">
         <v>7000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1469,16 +1536,22 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>100</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1494,33 +1567,33 @@
       <c r="G21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>6500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1539,11 +1612,17 @@
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1559,20 +1638,20 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1587,93 +1666,105 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
-        <v>100</v>
-      </c>
-      <c r="S22" s="3">
-        <v>100</v>
-      </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>6500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1716,17 +1807,17 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1737,8 +1828,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1899,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>6500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>6500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,16 +2112,22 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2027,31 +2148,31 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N29" s="3">
         <v>-100</v>
       </c>
       <c r="O29" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2062,8 +2183,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,8 +2325,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2204,38 +2343,38 @@
         <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
       </c>
       <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-7000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2249,81 +2388,93 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>100</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>6400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2538,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>6400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,59 +2743,61 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>11400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1900</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3">
-        <v>100</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
@@ -2632,55 +2805,61 @@
         <v>100</v>
       </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
+        <v>100</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F42" s="3">
         <v>8600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>9800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>6000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>100</v>
-      </c>
       <c r="I42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>100</v>
+      </c>
+      <c r="K42" s="3">
+        <v>100</v>
+      </c>
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>600</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -2694,24 +2873,30 @@
         <v>0</v>
       </c>
       <c r="U42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="W42" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>100</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>100</v>
@@ -2719,20 +2904,20 @@
       <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
+      <c r="H43" s="3">
+        <v>100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>100</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2744,22 +2929,22 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
+      <c r="T43" s="3">
+        <v>200</v>
+      </c>
+      <c r="U43" s="3">
+        <v>200</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
@@ -2767,8 +2952,14 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2796,44 +2987,50 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
+      <c r="L44" s="3">
+        <v>0</v>
       </c>
       <c r="M44" s="3">
-        <v>100</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
         <v>200</v>
       </c>
       <c r="T44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2841,22 +3038,22 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3">
         <v>600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
@@ -2865,7 +3062,7 @@
         <v>200</v>
       </c>
       <c r="M45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
@@ -2874,17 +3071,17 @@
         <v>200</v>
       </c>
       <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>200</v>
+      </c>
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
@@ -2897,73 +3094,85 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F46" s="3">
         <v>8900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>11600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>8900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2976,14 +3185,14 @@
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>100</v>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
         <v>100</v>
@@ -2994,11 +3203,11 @@
       <c r="L47" s="3">
         <v>100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
+      <c r="M47" s="3">
+        <v>100</v>
+      </c>
+      <c r="N47" s="3">
+        <v>100</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
@@ -3012,14 +3221,14 @@
       <c r="R47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>200</v>
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V47" s="3">
         <v>200</v>
@@ -3027,8 +3236,14 @@
       <c r="W47" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3092,8 +3307,14 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3157,8 +3378,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3520,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3308,10 +3547,10 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3325,17 +3564,17 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
+      <c r="R52" s="3">
+        <v>100</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
@@ -3352,8 +3591,14 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,58 +3662,64 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F54" s="3">
         <v>9000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>13000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>9000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>11400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2800</v>
-      </c>
-      <c r="R54" s="3">
-        <v>400</v>
-      </c>
-      <c r="S54" s="3">
-        <v>500</v>
       </c>
       <c r="T54" s="3">
         <v>400</v>
@@ -3477,13 +3728,19 @@
         <v>500</v>
       </c>
       <c r="V54" s="3">
+        <v>400</v>
+      </c>
+      <c r="W54" s="3">
+        <v>500</v>
+      </c>
+      <c r="X54" s="3">
         <v>800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,49 +3791,51 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
       </c>
       <c r="K57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
       <c r="M57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
       </c>
       <c r="O57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
@@ -3589,16 +3850,22 @@
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3645,16 +3912,16 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3">
-        <v>100</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3662,8 +3929,14 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3700,17 +3973,17 @@
       <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
+      <c r="O59" s="3">
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
+        <v>100</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
@@ -3721,70 +3994,76 @@
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
+      <c r="V59" s="3">
+        <v>0</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E60" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="F60" s="3">
         <v>700</v>
       </c>
       <c r="G60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H60" s="3">
+        <v>700</v>
+      </c>
+      <c r="I60" s="3">
         <v>400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>300</v>
       </c>
       <c r="J60" s="3">
         <v>300</v>
       </c>
       <c r="K60" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="L60" s="3">
         <v>300</v>
       </c>
       <c r="M60" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="N60" s="3">
         <v>300</v>
       </c>
       <c r="O60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q60" s="3">
         <v>100</v>
       </c>
       <c r="R60" s="3">
+        <v>100</v>
+      </c>
+      <c r="S60" s="3">
+        <v>100</v>
+      </c>
+      <c r="T60" s="3">
         <v>300</v>
       </c>
-      <c r="S60" s="3">
-        <v>100</v>
-      </c>
-      <c r="T60" s="3">
-        <v>100</v>
-      </c>
       <c r="U60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V60" s="3">
         <v>100</v>
@@ -3792,8 +4071,14 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3857,8 +4142,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3872,10 +4163,10 @@
         <v>800</v>
       </c>
       <c r="G62" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="H62" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I62" s="3">
         <v>900</v>
@@ -3887,20 +4178,20 @@
         <v>900</v>
       </c>
       <c r="L62" s="3">
+        <v>900</v>
+      </c>
+      <c r="M62" s="3">
+        <v>900</v>
+      </c>
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>900</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3913,17 +4204,23 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,64 +4426,70 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F66" s="3">
         <v>1500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1200</v>
       </c>
       <c r="J66" s="3">
         <v>1200</v>
       </c>
       <c r="K66" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="L66" s="3">
         <v>1200</v>
       </c>
       <c r="M66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N66" s="3">
         <v>1200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P66" s="3">
         <v>1300</v>
       </c>
-      <c r="O66" s="3">
-        <v>100</v>
-      </c>
-      <c r="P66" s="3">
-        <v>100</v>
-      </c>
       <c r="Q66" s="3">
         <v>100</v>
       </c>
       <c r="R66" s="3">
+        <v>100</v>
+      </c>
+      <c r="S66" s="3">
+        <v>100</v>
+      </c>
+      <c r="T66" s="3">
         <v>300</v>
       </c>
-      <c r="S66" s="3">
-        <v>100</v>
-      </c>
-      <c r="T66" s="3">
-        <v>100</v>
-      </c>
       <c r="U66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V66" s="3">
         <v>100</v>
@@ -4182,8 +4497,14 @@
       <c r="W66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4382,10 +4717,10 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>400</v>
@@ -4402,8 +4737,14 @@
       <c r="W70" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4808,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-9800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-9100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-8100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-7200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-5500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-4500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-3300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-2200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-8600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-8100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-5800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-4300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-2900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-2700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-2300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-2000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-1800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +5092,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F76" s="3">
         <v>7500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>11900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>10200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-300</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
+        <v>0</v>
+      </c>
+      <c r="V76" s="3">
         <v>-100</v>
       </c>
-      <c r="U76" s="3">
-        <v>100</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
+        <v>100</v>
+      </c>
+      <c r="X76" s="3">
         <v>300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5234,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>6400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5412,10 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5073,17 +5470,23 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,43 +5834,49 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-300</v>
       </c>
       <c r="O89" s="3">
         <v>-500</v>
@@ -5452,28 +5885,34 @@
         <v>-300</v>
       </c>
       <c r="Q89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,8 +5936,10 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5562,8 +6003,14 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +6145,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F94" s="3">
         <v>1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-6000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>100</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>6800</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>100</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>100</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6247,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,32 +6527,38 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>4900</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -6078,37 +6569,43 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>3800</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,69 +6669,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E102" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-4500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-6700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>6100</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N102" s="3">
-        <v>3500</v>
       </c>
       <c r="O102" s="3">
         <v>-500</v>
       </c>
       <c r="P102" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1900</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S102" s="3">
-        <v>100</v>
       </c>
       <c r="T102" s="3">
         <v>-100</v>
       </c>
       <c r="U102" s="3">
+        <v>100</v>
+      </c>
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>SILO</t>
   </si>
@@ -656,114 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -833,8 +837,11 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -878,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
@@ -895,8 +902,8 @@
       <c r="V9" s="3">
         <v>0</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
+      <c r="W9" s="3">
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>4</v>
@@ -904,8 +911,11 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -949,11 +959,11 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
         <v>-100</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
       <c r="S10" s="3">
         <v>0</v>
       </c>
@@ -966,8 +976,8 @@
       <c r="V10" s="3">
         <v>0</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
+      <c r="W10" s="3">
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>4</v>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,44 +1015,45 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E12" s="3">
         <v>300</v>
       </c>
       <c r="F12" s="3">
+        <v>300</v>
+      </c>
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
-        <v>100</v>
-      </c>
       <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
-        <v>100</v>
-      </c>
       <c r="L12" s="3">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
-        <v>100</v>
-      </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
@@ -1047,7 +1061,7 @@
         <v>100</v>
       </c>
       <c r="Q12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12" s="3">
         <v>0</v>
@@ -1059,10 +1073,10 @@
         <v>0</v>
       </c>
       <c r="U12" s="3">
-        <v>100</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
+        <v>100</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>4</v>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1164,8 +1184,8 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1173,11 +1193,11 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1185,26 +1205,26 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>4</v>
@@ -1212,11 +1232,14 @@
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,67 +1336,68 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
         <v>900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>500</v>
       </c>
       <c r="L17" s="3">
         <v>500</v>
       </c>
       <c r="M17" s="3">
+        <v>500</v>
+      </c>
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>600</v>
       </c>
       <c r="R17" s="3">
         <v>600</v>
       </c>
       <c r="S17" s="3">
+        <v>600</v>
+      </c>
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
-      </c>
-      <c r="V17" s="3">
-        <v>200</v>
       </c>
       <c r="W17" s="3">
         <v>200</v>
@@ -1379,10 +1406,13 @@
         <v>200</v>
       </c>
       <c r="Y17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1390,58 +1420,58 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-500</v>
       </c>
       <c r="L18" s="3">
         <v>-500</v>
       </c>
       <c r="M18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-600</v>
       </c>
       <c r="R18" s="3">
         <v>-600</v>
       </c>
       <c r="S18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-200</v>
       </c>
       <c r="W18" s="3">
         <v>-200</v>
@@ -1450,10 +1480,13 @@
         <v>-200</v>
       </c>
       <c r="Y18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1512,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1497,16 +1531,16 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>-100</v>
@@ -1515,16 +1549,16 @@
         <v>-100</v>
       </c>
       <c r="N20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O20" s="3">
         <v>7000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1542,16 +1576,19 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>100</v>
-      </c>
       <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1573,30 +1610,30 @@
       <c r="I21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>6500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1618,11 +1655,14 @@
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1644,8 +1684,8 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1653,8 +1693,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1672,16 +1712,16 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
-        <v>100</v>
-      </c>
       <c r="U22" s="3">
         <v>100</v>
       </c>
       <c r="V22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1689,87 +1729,93 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-600</v>
       </c>
       <c r="R23" s="3">
         <v>-600</v>
       </c>
       <c r="S23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T23" s="3">
         <v>-1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1813,14 +1859,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1834,8 +1880,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-600</v>
       </c>
       <c r="R26" s="3">
         <v>-600</v>
       </c>
       <c r="S26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-600</v>
       </c>
       <c r="R27" s="3">
         <v>-600</v>
       </c>
       <c r="S27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T27" s="3">
         <v>-1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,20 +2176,23 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
@@ -2154,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3">
         <v>-100</v>
@@ -2163,19 +2224,19 @@
         <v>-100</v>
       </c>
       <c r="Q29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2398,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2349,16 +2419,16 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>100</v>
@@ -2367,17 +2437,17 @@
         <v>100</v>
       </c>
       <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-7000</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2394,87 +2464,93 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,123 +2831,127 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>200</v>
       </c>
       <c r="G41" s="3">
         <v>200</v>
       </c>
       <c r="H41" s="3">
+        <v>200</v>
+      </c>
+      <c r="I41" s="3">
         <v>4700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1900</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="3">
         <v>200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4100</v>
+        <v>3100</v>
       </c>
       <c r="E42" s="3">
         <v>4100</v>
       </c>
       <c r="F42" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G42" s="3">
         <v>8600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
       </c>
       <c r="L42" s="3">
+        <v>100</v>
+      </c>
+      <c r="M42" s="3">
         <v>300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>800</v>
-      </c>
-      <c r="O42" s="3">
-        <v>600</v>
       </c>
       <c r="P42" s="3">
         <v>600</v>
       </c>
       <c r="Q42" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2879,27 +2969,30 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
@@ -2910,8 +3003,8 @@
       <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+      <c r="J43" s="3">
+        <v>100</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -2919,8 +3012,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2935,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>200</v>
@@ -2946,8 +3039,8 @@
       <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
+      <c r="V43" s="3">
+        <v>200</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
@@ -2958,8 +3051,11 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2993,14 +3089,14 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
-        <v>100</v>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3009,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
         <v>200</v>
@@ -3018,10 +3114,10 @@
         <v>200</v>
       </c>
       <c r="V44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -3029,8 +3125,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3038,34 +3137,34 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
       <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
       <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
-        <v>100</v>
-      </c>
       <c r="L45" s="3">
+        <v>100</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
-        <v>100</v>
-      </c>
       <c r="N45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
@@ -3077,14 +3176,14 @@
         <v>200</v>
       </c>
       <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
@@ -3100,79 +3199,85 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3191,11 +3296,11 @@
       <c r="H47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I47" s="3">
-        <v>0</v>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
@@ -3209,8 +3314,8 @@
       <c r="N47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
+      <c r="O47" s="3">
+        <v>100</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
@@ -3227,11 +3332,11 @@
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W47" s="3">
         <v>200</v>
@@ -3242,8 +3347,11 @@
       <c r="Y47" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3313,31 +3421,34 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3643,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3553,7 +3673,7 @@
         <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3570,14 +3690,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3">
-        <v>100</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" s="3">
+        <v>100</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,31 +3923,32 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>200</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
@@ -3826,10 +3957,10 @@
         <v>200</v>
       </c>
       <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
-      </c>
-      <c r="N57" s="3">
-        <v>200</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
@@ -3838,7 +3969,7 @@
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
@@ -3856,7 +3987,7 @@
         <v>100</v>
       </c>
       <c r="W57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
@@ -3864,8 +3995,11 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3918,13 +4052,13 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3">
-        <v>100</v>
-      </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3935,8 +4069,11 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3979,8 +4116,8 @@
       <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
+      <c r="Q59" s="3">
+        <v>100</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
@@ -3988,17 +4125,17 @@
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>4</v>
@@ -4006,31 +4143,34 @@
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E60" s="3">
         <v>900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>300</v>
       </c>
       <c r="K60" s="3">
         <v>300</v>
@@ -4039,10 +4179,10 @@
         <v>300</v>
       </c>
       <c r="M60" s="3">
+        <v>300</v>
+      </c>
+      <c r="N60" s="3">
         <v>500</v>
-      </c>
-      <c r="N60" s="3">
-        <v>300</v>
       </c>
       <c r="O60" s="3">
         <v>300</v>
@@ -4051,7 +4191,7 @@
         <v>300</v>
       </c>
       <c r="Q60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R60" s="3">
         <v>100</v>
@@ -4060,25 +4200,28 @@
         <v>100</v>
       </c>
       <c r="T60" s="3">
+        <v>100</v>
+      </c>
+      <c r="U60" s="3">
         <v>300</v>
       </c>
-      <c r="U60" s="3">
-        <v>100</v>
-      </c>
       <c r="V60" s="3">
         <v>100</v>
       </c>
       <c r="W60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4148,8 +4291,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4169,7 +4315,7 @@
         <v>800</v>
       </c>
       <c r="I62" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J62" s="3">
         <v>900</v>
@@ -4184,17 +4330,17 @@
         <v>900</v>
       </c>
       <c r="N62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="O62" s="3">
         <v>1000</v>
       </c>
       <c r="P62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4210,8 +4356,8 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,31 +4587,34 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="E66" s="3">
         <v>1600</v>
       </c>
       <c r="F66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G66" s="3">
         <v>1500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1200</v>
       </c>
       <c r="K66" s="3">
         <v>1200</v>
@@ -4465,20 +4623,20 @@
         <v>1200</v>
       </c>
       <c r="M66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N66" s="3">
         <v>1400</v>
-      </c>
-      <c r="N66" s="3">
-        <v>1200</v>
       </c>
       <c r="O66" s="3">
         <v>1200</v>
       </c>
       <c r="P66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1300</v>
       </c>
-      <c r="Q66" s="3">
-        <v>100</v>
-      </c>
       <c r="R66" s="3">
         <v>100</v>
       </c>
@@ -4486,25 +4644,28 @@
         <v>100</v>
       </c>
       <c r="T66" s="3">
+        <v>100</v>
+      </c>
+      <c r="U66" s="3">
         <v>300</v>
       </c>
-      <c r="U66" s="3">
-        <v>100</v>
-      </c>
       <c r="V66" s="3">
         <v>100</v>
       </c>
       <c r="W66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4723,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>400</v>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-9800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-300</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
       <c r="V76" s="3">
+        <v>0</v>
+      </c>
+      <c r="W76" s="3">
         <v>-100</v>
       </c>
-      <c r="W76" s="3">
-        <v>100</v>
-      </c>
       <c r="X76" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y76" s="3">
         <v>300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5476,17 +5675,20 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-800</v>
       </c>
       <c r="M89" s="3">
         <v>-800</v>
       </c>
       <c r="N89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-200</v>
       </c>
       <c r="W89" s="3">
         <v>-200</v>
       </c>
       <c r="X89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6158,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,47 +6378,50 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E94" s="3">
+        <v>100</v>
+      </c>
+      <c r="F94" s="3">
         <v>4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6000</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>6800</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -6201,29 +6431,32 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V94" s="3">
-        <v>100</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>100</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,35 +6776,38 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>4900</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -6575,26 +6821,26 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>3800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>2100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -6604,8 +6850,11 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3300</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-4500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
-        <v>100</v>
-      </c>
       <c r="V102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="W102" s="3">
         <v>-100</v>
       </c>
       <c r="X102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>SILO</t>
   </si>
@@ -656,118 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -780,8 +784,8 @@
       <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
@@ -840,8 +844,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -854,8 +861,8 @@
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
+      <c r="G9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -888,10 +895,10 @@
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
@@ -905,8 +912,8 @@
       <c r="W9" s="3">
         <v>0</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>4</v>
+      <c r="X9" s="3">
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>4</v>
@@ -914,13 +921,16 @@
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -928,8 +938,8 @@
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -962,11 +972,11 @@
         <v>0</v>
       </c>
       <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
         <v>-100</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
       <c r="T10" s="3">
         <v>0</v>
       </c>
@@ -979,8 +989,8 @@
       <c r="W10" s="3">
         <v>0</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>4</v>
+      <c r="X10" s="3">
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>4</v>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,47 +1029,48 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>400</v>
-      </c>
-      <c r="E12" s="3">
-        <v>300</v>
       </c>
       <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
-        <v>100</v>
-      </c>
       <c r="I12" s="3">
+        <v>100</v>
+      </c>
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
-        <v>100</v>
-      </c>
       <c r="M12" s="3">
+        <v>100</v>
+      </c>
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
-        <v>100</v>
-      </c>
       <c r="P12" s="3">
         <v>100</v>
       </c>
@@ -1064,7 +1078,7 @@
         <v>100</v>
       </c>
       <c r="R12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12" s="3">
         <v>0</v>
@@ -1076,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="V12" s="3">
-        <v>100</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <v>100</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>4</v>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,31 +1181,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1196,11 +1216,11 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1208,26 +1228,26 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
@@ -1235,11 +1255,14 @@
       <c r="Y14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z14" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,8 +1363,9 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1346,61 +1373,61 @@
         <v>1000</v>
       </c>
       <c r="E17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>500</v>
       </c>
       <c r="M17" s="3">
         <v>500</v>
       </c>
       <c r="N17" s="3">
+        <v>500</v>
+      </c>
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
-      </c>
-      <c r="R17" s="3">
-        <v>600</v>
       </c>
       <c r="S17" s="3">
         <v>600</v>
       </c>
       <c r="T17" s="3">
+        <v>600</v>
+      </c>
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
-      </c>
-      <c r="W17" s="3">
-        <v>200</v>
       </c>
       <c r="X17" s="3">
         <v>200</v>
@@ -1409,72 +1436,75 @@
         <v>200</v>
       </c>
       <c r="Z17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-1000</v>
       </c>
       <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-500</v>
       </c>
       <c r="M18" s="3">
         <v>-500</v>
       </c>
       <c r="N18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-600</v>
       </c>
       <c r="S18" s="3">
         <v>-600</v>
       </c>
       <c r="T18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-200</v>
       </c>
       <c r="X18" s="3">
         <v>-200</v>
@@ -1483,10 +1513,13 @@
         <v>-200</v>
       </c>
       <c r="Z18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,37 +1546,38 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-100</v>
@@ -1552,16 +1586,16 @@
         <v>-100</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
         <v>7000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1579,64 +1613,67 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>100</v>
-      </c>
       <c r="Z20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="D21" s="3">
         <v>-1000</v>
       </c>
+      <c r="E21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="L21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>6500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1658,11 +1695,14 @@
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1675,8 +1715,8 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1687,8 +1727,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
@@ -1696,8 +1736,8 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1715,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
-        <v>100</v>
-      </c>
       <c r="V22" s="3">
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1732,11 +1772,14 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1744,96 +1787,99 @@
         <v>-900</v>
       </c>
       <c r="E23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="P23" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R23" s="3">
         <v>-900</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>6500</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-600</v>
       </c>
       <c r="S23" s="3">
         <v>-600</v>
       </c>
       <c r="T23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U23" s="3">
         <v>-1400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1862,14 +1908,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>4</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1883,8 +1929,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,8 +2006,11 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1966,73 +2018,76 @@
         <v>-900</v>
       </c>
       <c r="E26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="P26" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R26" s="3">
         <v>-900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O26" s="3">
-        <v>6500</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-600</v>
       </c>
       <c r="S26" s="3">
         <v>-600</v>
       </c>
       <c r="T26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U26" s="3">
         <v>-1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2040,73 +2095,76 @@
         <v>-900</v>
       </c>
       <c r="E27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-600</v>
       </c>
       <c r="S27" s="3">
         <v>-600</v>
       </c>
       <c r="T27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U27" s="3">
         <v>-1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,19 +2237,22 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>4</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -2218,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3">
         <v>-100</v>
@@ -2227,19 +2288,19 @@
         <v>-100</v>
       </c>
       <c r="R29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S29" s="3">
         <v>-200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,82 +2468,88 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2484,73 +2557,76 @@
         <v>-900</v>
       </c>
       <c r="E33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="P33" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O33" s="3">
-        <v>6400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-800</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,8 +2699,11 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2632,152 +2711,158 @@
         <v>-900</v>
       </c>
       <c r="E35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="P35" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O35" s="3">
-        <v>6400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-800</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,129 +2918,133 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E41" s="3">
         <v>4500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3500</v>
-      </c>
-      <c r="G41" s="3">
-        <v>200</v>
       </c>
       <c r="H41" s="3">
         <v>200</v>
       </c>
       <c r="I41" s="3">
+        <v>200</v>
+      </c>
+      <c r="J41" s="3">
         <v>4700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1900</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E42" s="3">
         <v>3100</v>
-      </c>
-      <c r="E42" s="3">
-        <v>4100</v>
       </c>
       <c r="F42" s="3">
         <v>4100</v>
       </c>
       <c r="G42" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H42" s="3">
         <v>8600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>100</v>
       </c>
       <c r="M42" s="3">
+        <v>100</v>
+      </c>
+      <c r="N42" s="3">
         <v>300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>800</v>
-      </c>
-      <c r="P42" s="3">
-        <v>600</v>
       </c>
       <c r="Q42" s="3">
         <v>600</v>
       </c>
       <c r="R42" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2972,30 +3062,33 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
@@ -3006,8 +3099,8 @@
       <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
+      <c r="K43" s="3">
+        <v>100</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
@@ -3015,8 +3108,8 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3031,10 +3124,10 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>200</v>
@@ -3042,8 +3135,8 @@
       <c r="V43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
+      <c r="W43" s="3">
+        <v>200</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>4</v>
@@ -3054,31 +3147,34 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3092,14 +3188,14 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P44" s="3">
-        <v>100</v>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3108,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3">
         <v>200</v>
@@ -3117,10 +3213,10 @@
         <v>200</v>
       </c>
       <c r="W44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3128,46 +3224,49 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
+        <v>100</v>
+      </c>
+      <c r="L45" s="3">
+        <v>600</v>
+      </c>
+      <c r="M45" s="3">
+        <v>100</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
-        <v>100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>100</v>
-      </c>
       <c r="O45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
@@ -3179,14 +3278,14 @@
         <v>200</v>
       </c>
       <c r="S45" s="3">
+        <v>200</v>
+      </c>
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>500</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
@@ -3202,82 +3301,88 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E46" s="3">
         <v>7700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3299,11 +3404,11 @@
       <c r="I47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L47" s="3">
         <v>100</v>
@@ -3317,8 +3422,8 @@
       <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
+      <c r="P47" s="3">
+        <v>100</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
@@ -3335,11 +3440,11 @@
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X47" s="3">
         <v>200</v>
@@ -3350,31 +3455,34 @@
       <c r="Z47" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -3424,34 +3532,37 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
         <v>200</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="E49" s="3">
+        <v>200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,37 +3763,40 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3693,14 +3813,14 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="3">
-        <v>100</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3">
+        <v>100</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E54" s="3">
         <v>8000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,25 +4054,26 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1000</v>
       </c>
       <c r="I57" s="3">
         <v>700</v>
@@ -3951,7 +4082,7 @@
         <v>400</v>
       </c>
       <c r="K57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
@@ -3960,10 +4091,10 @@
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
@@ -3972,7 +4103,7 @@
         <v>200</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
@@ -3990,7 +4121,7 @@
         <v>100</v>
       </c>
       <c r="X57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
@@ -3998,8 +4129,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4055,13 +4189,13 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3">
-        <v>100</v>
-      </c>
       <c r="W58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4072,8 +4206,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4119,8 +4256,8 @@
       <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
+      <c r="R59" s="3">
+        <v>100</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
@@ -4128,17 +4265,17 @@
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
@@ -4146,34 +4283,37 @@
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>400</v>
-      </c>
-      <c r="K60" s="3">
-        <v>300</v>
       </c>
       <c r="L60" s="3">
         <v>300</v>
@@ -4182,10 +4322,10 @@
         <v>300</v>
       </c>
       <c r="N60" s="3">
+        <v>300</v>
+      </c>
+      <c r="O60" s="3">
         <v>500</v>
-      </c>
-      <c r="O60" s="3">
-        <v>300</v>
       </c>
       <c r="P60" s="3">
         <v>300</v>
@@ -4194,7 +4334,7 @@
         <v>300</v>
       </c>
       <c r="R60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
@@ -4203,25 +4343,28 @@
         <v>100</v>
       </c>
       <c r="U60" s="3">
+        <v>100</v>
+      </c>
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="V60" s="3">
-        <v>100</v>
-      </c>
       <c r="W60" s="3">
         <v>100</v>
       </c>
       <c r="X60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4294,31 +4437,34 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>900</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>900</v>
@@ -4333,17 +4479,17 @@
         <v>900</v>
       </c>
       <c r="O62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="P62" s="3">
         <v>1000</v>
       </c>
       <c r="Q62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4359,8 +4505,8 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,34 +4745,37 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2100</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1600</v>
       </c>
       <c r="F66" s="3">
         <v>1600</v>
       </c>
       <c r="G66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1200</v>
       </c>
       <c r="L66" s="3">
         <v>1200</v>
@@ -4626,20 +4784,20 @@
         <v>1200</v>
       </c>
       <c r="N66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O66" s="3">
         <v>1400</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1200</v>
       </c>
       <c r="P66" s="3">
         <v>1200</v>
       </c>
       <c r="Q66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R66" s="3">
         <v>1300</v>
       </c>
-      <c r="R66" s="3">
-        <v>100</v>
-      </c>
       <c r="S66" s="3">
         <v>100</v>
       </c>
@@ -4647,25 +4805,28 @@
         <v>100</v>
       </c>
       <c r="U66" s="3">
+        <v>100</v>
+      </c>
+      <c r="V66" s="3">
         <v>300</v>
       </c>
-      <c r="V66" s="3">
-        <v>100</v>
-      </c>
       <c r="W66" s="3">
         <v>100</v>
       </c>
       <c r="X66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4894,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>400</v>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-12600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-10900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-9800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-9100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E76" s="3">
         <v>6000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-300</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
       <c r="W76" s="3">
+        <v>0</v>
+      </c>
+      <c r="X76" s="3">
         <v>-100</v>
       </c>
-      <c r="X76" s="3">
-        <v>100</v>
-      </c>
       <c r="Y76" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z76" s="3">
         <v>300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,87 +5621,93 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5520,73 +5715,76 @@
         <v>-900</v>
       </c>
       <c r="E81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="P81" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-600</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O81" s="3">
-        <v>6400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-800</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,31 +5811,32 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5678,17 +5877,20 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-800</v>
       </c>
       <c r="N89" s="3">
         <v>-800</v>
       </c>
       <c r="O89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-200</v>
       </c>
       <c r="X89" s="3">
         <v>-200</v>
       </c>
       <c r="Y89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,31 +6379,32 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,50 +6608,53 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>1000</v>
       </c>
-      <c r="E94" s="3">
-        <v>100</v>
-      </c>
       <c r="F94" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G94" s="3">
+        <v>100</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
         <v>1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>6800</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
@@ -6434,29 +6664,32 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W94" s="3">
-        <v>100</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>100</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,31 +6716,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,38 +7022,41 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>4900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -6824,26 +7070,26 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>3800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>2100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -6853,31 +7099,34 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6927,78 +7176,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
-        <v>3300</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-4500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
-        <v>100</v>
-      </c>
       <c r="W102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="X102" s="3">
         <v>-100</v>
       </c>
       <c r="Y102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>SILO</t>
   </si>
@@ -656,122 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -784,14 +791,14 @@
       <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
+      <c r="G8" s="3">
+        <v>0</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -847,8 +854,14 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -861,14 +874,14 @@
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
+      <c r="I9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -898,13 +911,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
@@ -915,17 +928,23 @@
       <c r="X9" s="3">
         <v>0</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>4</v>
+      <c r="Y9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>0</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -938,14 +957,14 @@
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
+      <c r="I10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -975,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>-100</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
         <v>0</v>
       </c>
@@ -992,17 +1011,23 @@
       <c r="X10" s="3">
         <v>0</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>4</v>
+      <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>0</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,61 +1055,63 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3">
-        <v>200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>100</v>
+      <c r="I12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J12" s="3">
         <v>200</v>
       </c>
       <c r="K12" s="3">
+        <v>100</v>
+      </c>
+      <c r="L12" s="3">
+        <v>200</v>
+      </c>
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
-        <v>100</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
-      </c>
       <c r="R12" s="3">
         <v>100</v>
       </c>
       <c r="S12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
@@ -1093,13 +1120,13 @@
         <v>0</v>
       </c>
       <c r="W12" s="3">
-        <v>100</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>100</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>4</v>
@@ -1107,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,85 +1217,97 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>4</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA14" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F17" s="3">
         <v>1000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="3">
-        <v>800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1100</v>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J17" s="3">
         <v>800</v>
       </c>
       <c r="K17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L17" s="3">
+        <v>800</v>
+      </c>
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>500</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1000</v>
       </c>
       <c r="P17" s="3">
         <v>500</v>
       </c>
       <c r="Q17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>500</v>
+      </c>
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1200</v>
-      </c>
-      <c r="V17" s="3">
-        <v>200</v>
-      </c>
-      <c r="W17" s="3">
-        <v>400</v>
       </c>
       <c r="X17" s="3">
         <v>200</v>
       </c>
       <c r="Y17" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Z17" s="3">
         <v>200</v>
       </c>
       <c r="AA17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1100</v>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J18" s="3">
         <v>-800</v>
       </c>
       <c r="K18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1000</v>
       </c>
       <c r="P18" s="3">
         <v>-500</v>
       </c>
       <c r="Q18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-400</v>
       </c>
       <c r="X18" s="3">
         <v>-200</v>
       </c>
       <c r="Y18" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="Z18" s="3">
         <v>-200</v>
       </c>
       <c r="AA18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,13 +1612,15 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1561,11 +1628,11 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
@@ -1573,35 +1640,35 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R20" s="3">
         <v>7000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1616,70 +1683,76 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-800</v>
-      </c>
       <c r="I21" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
+      <c r="K21" s="3">
+        <v>-1100</v>
       </c>
       <c r="L21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>-1000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>6500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1698,11 +1771,17 @@
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1715,14 +1794,14 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1730,20 +1809,20 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1758,105 +1837,117 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
-        <v>100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>100</v>
-      </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>6500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1881,11 +1972,11 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1911,17 +2002,17 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1932,8 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>6500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>6500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2282,31 +2403,31 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R29" s="3">
         <v>-100</v>
       </c>
       <c r="S29" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="T29" s="3">
         <v>-100</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="U29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,13 +2604,19 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2485,11 +2624,11 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
@@ -2497,36 +2636,36 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2540,93 +2679,105 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,71 +3090,73 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F41" s="3">
         <v>4900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>11400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>12300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>9800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>10300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1900</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3">
-        <v>100</v>
-      </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
@@ -2991,67 +3164,73 @@
         <v>100</v>
       </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E42" s="3">
         <v>3200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G42" s="3">
         <v>3100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>4100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>4100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>8600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>9800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>6000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>100</v>
-      </c>
       <c r="M42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>100</v>
+      </c>
+      <c r="O42" s="3">
+        <v>100</v>
+      </c>
+      <c r="P42" s="3">
         <v>300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>600</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
@@ -3065,21 +3244,27 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -3091,10 +3276,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -3102,20 +3287,20 @@
       <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
+      <c r="L43" s="3">
+        <v>100</v>
+      </c>
+      <c r="M43" s="3">
+        <v>100</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3127,22 +3312,22 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
+      <c r="X43" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>200</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>4</v>
@@ -3150,8 +3335,14 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3176,11 +3367,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3191,49 +3382,55 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
+      <c r="P44" s="3">
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
       </c>
       <c r="U44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3">
         <v>200</v>
       </c>
       <c r="X44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -3254,16 +3451,16 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
+        <v>100</v>
+      </c>
+      <c r="N45" s="3">
         <v>600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>200</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
@@ -3272,7 +3469,7 @@
         <v>200</v>
       </c>
       <c r="Q45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
@@ -3281,17 +3478,17 @@
         <v>200</v>
       </c>
       <c r="T45" s="3">
+        <v>200</v>
+      </c>
+      <c r="U45" s="3">
+        <v>200</v>
+      </c>
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
@@ -3304,85 +3501,97 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F46" s="3">
         <v>8300</v>
-      </c>
-      <c r="E46" s="3">
-        <v>7700</v>
-      </c>
-      <c r="F46" s="3">
-        <v>6900</v>
       </c>
       <c r="G46" s="3">
         <v>7700</v>
       </c>
       <c r="H46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="J46" s="3">
         <v>8900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>11000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>8900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>9600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>11300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3407,14 +3616,14 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>100</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>100</v>
@@ -3425,11 +3634,11 @@
       <c r="P47" s="3">
         <v>100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
+      <c r="Q47" s="3">
+        <v>100</v>
+      </c>
+      <c r="R47" s="3">
+        <v>100</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
@@ -3443,14 +3652,14 @@
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
-      <c r="X47" s="3">
-        <v>200</v>
+      <c r="W47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="3">
         <v>200</v>
@@ -3458,8 +3667,14 @@
       <c r="AA47" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3484,11 +3699,11 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -3535,8 +3750,14 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3547,10 +3768,10 @@
         <v>200</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -3561,14 +3782,14 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3612,8 +3833,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,22 +3999,28 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
@@ -3792,17 +4031,17 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>100</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3816,17 +4055,17 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
+      <c r="V52" s="3">
+        <v>100</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
@@ -3843,8 +4082,14 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,70 +4165,76 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F54" s="3">
         <v>8600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>13000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>9000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>10500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>11400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2800</v>
-      </c>
-      <c r="V54" s="3">
-        <v>400</v>
-      </c>
-      <c r="W54" s="3">
-        <v>500</v>
       </c>
       <c r="X54" s="3">
         <v>400</v>
@@ -3992,13 +4243,19 @@
         <v>500</v>
       </c>
       <c r="Z54" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB54" s="3">
         <v>800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,61 +4314,63 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>600</v>
       </c>
       <c r="I57" s="3">
         <v>700</v>
       </c>
       <c r="J57" s="3">
+        <v>600</v>
+      </c>
+      <c r="K57" s="3">
+        <v>700</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
       </c>
       <c r="O57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
       </c>
       <c r="S57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
@@ -4124,16 +4385,22 @@
         <v>100</v>
       </c>
       <c r="Y57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4192,16 +4459,16 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3">
-        <v>100</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4209,8 +4476,14 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4259,17 +4532,17 @@
       <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
+      <c r="S59" s="3">
+        <v>100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>100</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>4</v>
@@ -4280,82 +4553,88 @@
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
+      <c r="Z59" s="3">
+        <v>0</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F60" s="3">
         <v>1000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1100</v>
       </c>
       <c r="J60" s="3">
         <v>700</v>
       </c>
       <c r="K60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L60" s="3">
+        <v>700</v>
+      </c>
+      <c r="M60" s="3">
         <v>400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>300</v>
-      </c>
-      <c r="M60" s="3">
-        <v>300</v>
       </c>
       <c r="N60" s="3">
         <v>300</v>
       </c>
       <c r="O60" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="P60" s="3">
         <v>300</v>
       </c>
       <c r="Q60" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="R60" s="3">
         <v>300</v>
       </c>
       <c r="S60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="T60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U60" s="3">
         <v>100</v>
       </c>
       <c r="V60" s="3">
+        <v>100</v>
+      </c>
+      <c r="W60" s="3">
+        <v>100</v>
+      </c>
+      <c r="X60" s="3">
         <v>300</v>
       </c>
-      <c r="W60" s="3">
-        <v>100</v>
-      </c>
-      <c r="X60" s="3">
-        <v>100</v>
-      </c>
       <c r="Y60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z60" s="3">
         <v>100</v>
@@ -4363,8 +4642,14 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4440,8 +4725,14 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4466,11 +4757,11 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>900</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>900</v>
@@ -4482,20 +4773,20 @@
         <v>900</v>
       </c>
       <c r="P62" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>900</v>
+      </c>
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4508,17 +4799,23 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,76 +5057,82 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1300</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M66" s="3">
-        <v>1200</v>
       </c>
       <c r="N66" s="3">
         <v>1200</v>
       </c>
       <c r="O66" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="P66" s="3">
         <v>1200</v>
       </c>
       <c r="Q66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R66" s="3">
         <v>1200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T66" s="3">
         <v>1300</v>
       </c>
-      <c r="S66" s="3">
-        <v>100</v>
-      </c>
-      <c r="T66" s="3">
-        <v>100</v>
-      </c>
       <c r="U66" s="3">
         <v>100</v>
       </c>
       <c r="V66" s="3">
+        <v>100</v>
+      </c>
+      <c r="W66" s="3">
+        <v>100</v>
+      </c>
+      <c r="X66" s="3">
         <v>300</v>
       </c>
-      <c r="W66" s="3">
-        <v>100</v>
-      </c>
-      <c r="X66" s="3">
-        <v>100</v>
-      </c>
       <c r="Y66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z66" s="3">
         <v>100</v>
@@ -4825,8 +5140,14 @@
       <c r="AA66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5065,10 +5400,10 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>400</v>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-13500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-12600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-11700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-10900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-9800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-9100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-8100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-7200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-5500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-4500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-3900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-3300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-8600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-8100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-5800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-5000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-4300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-2900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-2700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F76" s="3">
         <v>6800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>10300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>10200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-300</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="3">
         <v>-100</v>
       </c>
-      <c r="Y76" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB76" s="3">
         <v>300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5838,11 +6235,11 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5880,17 +6277,23 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,55 +6701,61 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-300</v>
       </c>
       <c r="S89" s="3">
         <v>-500</v>
@@ -6331,28 +6764,34 @@
         <v>-300</v>
       </c>
       <c r="U89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6406,11 +6847,11 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6457,8 +6898,14 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +7064,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>1000</v>
       </c>
-      <c r="F94" s="3">
-        <v>100</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H94" s="3">
+        <v>100</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
         <v>1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>100</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>6800</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,11 +7210,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,44 +7510,50 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>4900</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -7073,37 +7564,43 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>3800</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>2100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,11 +7625,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7179,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-4500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>6100</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R102" s="3">
-        <v>3500</v>
       </c>
       <c r="S102" s="3">
         <v>-500</v>
       </c>
       <c r="T102" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1900</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W102" s="3">
-        <v>100</v>
       </c>
       <c r="X102" s="3">
         <v>-100</v>
       </c>
       <c r="Y102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>SILO</t>
   </si>
@@ -656,129 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -797,11 +801,11 @@
       <c r="H8" s="3">
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -860,8 +864,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -880,11 +887,11 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K9" s="3">
         <v>0</v>
@@ -917,11 +924,11 @@
         <v>0</v>
       </c>
       <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
         <v>100</v>
       </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
       <c r="W9" s="3">
         <v>0</v>
       </c>
@@ -934,8 +941,8 @@
       <c r="Z9" s="3">
         <v>0</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>4</v>
+      <c r="AA9" s="3">
+        <v>0</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>4</v>
@@ -943,8 +950,11 @@
       <c r="AC9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -963,11 +973,11 @@
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -1000,11 +1010,11 @@
         <v>0</v>
       </c>
       <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>-100</v>
       </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
       <c r="W10" s="3">
         <v>0</v>
       </c>
@@ -1017,8 +1027,8 @@
       <c r="Z10" s="3">
         <v>0</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>4</v>
+      <c r="AA10" s="3">
+        <v>0</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>4</v>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,55 +1070,56 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>700</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>500</v>
-      </c>
-      <c r="R12" s="3">
-        <v>100</v>
       </c>
       <c r="S12" s="3">
         <v>100</v>
@@ -1114,7 +1128,7 @@
         <v>100</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12" s="3">
         <v>0</v>
@@ -1126,11 +1140,11 @@
         <v>0</v>
       </c>
       <c r="Y12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="3">
         <v>100</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,41 +1254,41 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1276,26 +1296,26 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
+      <c r="Y14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>4</v>
@@ -1303,11 +1323,14 @@
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD14" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,79 +1443,80 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1000</v>
       </c>
       <c r="G17" s="3">
         <v>1000</v>
       </c>
       <c r="H17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>500</v>
       </c>
       <c r="P17" s="3">
         <v>500</v>
       </c>
       <c r="Q17" s="3">
+        <v>500</v>
+      </c>
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>900</v>
-      </c>
-      <c r="U17" s="3">
-        <v>600</v>
       </c>
       <c r="V17" s="3">
         <v>600</v>
       </c>
       <c r="W17" s="3">
+        <v>600</v>
+      </c>
+      <c r="X17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>400</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>200</v>
       </c>
       <c r="AA17" s="3">
         <v>200</v>
@@ -1498,81 +1525,84 @@
         <v>200</v>
       </c>
       <c r="AC17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1000</v>
       </c>
       <c r="G18" s="3">
         <v>-1000</v>
       </c>
       <c r="H18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-500</v>
       </c>
       <c r="P18" s="3">
         <v>-500</v>
       </c>
       <c r="Q18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-900</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-600</v>
       </c>
       <c r="V18" s="3">
         <v>-600</v>
       </c>
       <c r="W18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-200</v>
       </c>
       <c r="AA18" s="3">
         <v>-200</v>
@@ -1581,10 +1611,13 @@
         <v>-200</v>
       </c>
       <c r="AC18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,16 +1647,17 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1634,8 +1668,8 @@
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
@@ -1646,14 +1680,14 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>-100</v>
@@ -1662,17 +1696,17 @@
         <v>-100</v>
       </c>
       <c r="R20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S20" s="3">
         <v>7000</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1689,73 +1723,76 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-1000</v>
       </c>
       <c r="G21" s="3">
         <v>-1000</v>
       </c>
       <c r="H21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>6500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1777,11 +1814,14 @@
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1800,11 +1840,11 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1815,8 +1855,8 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>4</v>
@@ -1824,8 +1864,8 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1843,16 +1883,16 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
-      </c>
-      <c r="X22" s="3">
-        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1860,94 +1900,100 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-900</v>
       </c>
       <c r="G23" s="3">
         <v>-900</v>
       </c>
       <c r="H23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-900</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-600</v>
       </c>
       <c r="V23" s="3">
         <v>-600</v>
       </c>
       <c r="W23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X23" s="3">
         <v>-1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1978,8 +2024,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2008,14 +2054,14 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>4</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-900</v>
       </c>
       <c r="G26" s="3">
         <v>-900</v>
       </c>
       <c r="H26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-900</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-600</v>
       </c>
       <c r="V26" s="3">
         <v>-600</v>
       </c>
       <c r="W26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X26" s="3">
         <v>-1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-900</v>
       </c>
       <c r="G27" s="3">
         <v>-900</v>
       </c>
       <c r="H27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2300</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-600</v>
       </c>
       <c r="V27" s="3">
         <v>-600</v>
       </c>
       <c r="W27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X27" s="3">
         <v>-1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2409,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S29" s="3">
         <v>-100</v>
@@ -2418,19 +2479,19 @@
         <v>-100</v>
       </c>
       <c r="U29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-100</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,16 +2677,19 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2630,8 +2700,8 @@
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
@@ -2642,14 +2712,14 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>100</v>
@@ -2658,17 +2728,17 @@
         <v>100</v>
       </c>
       <c r="R32" s="3">
+        <v>100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-7000</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2685,99 +2755,105 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-900</v>
       </c>
       <c r="G33" s="3">
         <v>-900</v>
       </c>
       <c r="H33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-900</v>
       </c>
       <c r="G35" s="3">
         <v>-900</v>
       </c>
       <c r="H35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,147 +3178,151 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
         <v>3100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>200</v>
       </c>
       <c r="K41" s="3">
         <v>200</v>
       </c>
       <c r="L41" s="3">
+        <v>200</v>
+      </c>
+      <c r="M41" s="3">
         <v>4700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1900</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="3">
         <v>100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E42" s="3">
         <v>2300</v>
-      </c>
-      <c r="E42" s="3">
-        <v>3200</v>
       </c>
       <c r="F42" s="3">
         <v>3200</v>
       </c>
       <c r="G42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H42" s="3">
         <v>3100</v>
-      </c>
-      <c r="H42" s="3">
-        <v>4100</v>
       </c>
       <c r="I42" s="3">
         <v>4100</v>
       </c>
       <c r="J42" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K42" s="3">
         <v>8600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>100</v>
       </c>
       <c r="P42" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q42" s="3">
         <v>300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>800</v>
-      </c>
-      <c r="S42" s="3">
-        <v>600</v>
       </c>
       <c r="T42" s="3">
         <v>600</v>
       </c>
       <c r="U42" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3250,21 +3340,24 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -3282,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -3293,8 +3386,8 @@
       <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
+      <c r="N43" s="3">
+        <v>100</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>4</v>
@@ -3302,8 +3395,8 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3318,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>100</v>
-      </c>
-      <c r="W43" s="3">
-        <v>200</v>
       </c>
       <c r="X43" s="3">
         <v>200</v>
@@ -3329,8 +3422,8 @@
       <c r="Y43" s="3">
         <v>200</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
+      <c r="Z43" s="3">
+        <v>200</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>4</v>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3373,8 +3469,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3388,15 +3484,15 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S44" s="3">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
@@ -3404,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="W44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3">
         <v>200</v>
@@ -3413,24 +3509,27 @@
         <v>200</v>
       </c>
       <c r="Z44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA44" s="3">
         <v>100</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
-      </c>
       <c r="AB44" s="3">
         <v>0</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -3457,22 +3556,22 @@
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>200</v>
       </c>
       <c r="S45" s="3">
         <v>200</v>
@@ -3484,14 +3583,14 @@
         <v>200</v>
       </c>
       <c r="V45" s="3">
+        <v>200</v>
+      </c>
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
@@ -3507,91 +3606,97 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E46" s="3">
         <v>5600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3622,11 +3727,11 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
         <v>100</v>
@@ -3640,8 +3745,8 @@
       <c r="R47" s="3">
         <v>100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
+      <c r="S47" s="3">
+        <v>100</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
@@ -3658,11 +3763,11 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="3">
         <v>200</v>
@@ -3673,8 +3778,11 @@
       <c r="AC47" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3705,8 +3813,8 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3756,8 +3864,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3774,7 +3885,7 @@
         <v>200</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -3788,11 +3899,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,22 +4122,25 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
@@ -4037,14 +4157,14 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>100</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -4061,15 +4181,15 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,43 +4446,44 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>400</v>
       </c>
       <c r="M57" s="3">
         <v>400</v>
       </c>
       <c r="N57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
@@ -4361,10 +4492,10 @@
         <v>200</v>
       </c>
       <c r="Q57" s="3">
+        <v>200</v>
+      </c>
+      <c r="R57" s="3">
         <v>400</v>
-      </c>
-      <c r="R57" s="3">
-        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
@@ -4373,7 +4504,7 @@
         <v>200</v>
       </c>
       <c r="U57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
@@ -4391,7 +4522,7 @@
         <v>100</v>
       </c>
       <c r="AA57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
@@ -4399,8 +4530,11 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4465,14 +4599,14 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>100</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
@@ -4482,8 +4616,11 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4538,8 +4675,8 @@
       <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
+      <c r="U59" s="3">
+        <v>100</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>4</v>
@@ -4547,17 +4684,17 @@
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>4</v>
@@ -4565,43 +4702,46 @@
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
-      </c>
-      <c r="N60" s="3">
-        <v>300</v>
       </c>
       <c r="O60" s="3">
         <v>300</v>
@@ -4610,10 +4750,10 @@
         <v>300</v>
       </c>
       <c r="Q60" s="3">
+        <v>300</v>
+      </c>
+      <c r="R60" s="3">
         <v>500</v>
-      </c>
-      <c r="R60" s="3">
-        <v>300</v>
       </c>
       <c r="S60" s="3">
         <v>300</v>
@@ -4622,7 +4762,7 @@
         <v>300</v>
       </c>
       <c r="U60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="V60" s="3">
         <v>100</v>
@@ -4631,25 +4771,28 @@
         <v>100</v>
       </c>
       <c r="X60" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y60" s="3">
         <v>300</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>100</v>
       </c>
       <c r="Z60" s="3">
         <v>100</v>
       </c>
       <c r="AA60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="3">
         <v>100</v>
       </c>
-      <c r="AC60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4731,8 +4874,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4763,8 +4909,8 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>900</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>900</v>
@@ -4779,17 +4925,17 @@
         <v>900</v>
       </c>
       <c r="R62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="S62" s="3">
         <v>1000</v>
       </c>
       <c r="T62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U62" s="3">
         <v>900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
@@ -4805,8 +4951,8 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,43 +5218,46 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2100</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1600</v>
       </c>
       <c r="I66" s="3">
         <v>1600</v>
       </c>
       <c r="J66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K66" s="3">
         <v>1500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1300</v>
-      </c>
-      <c r="N66" s="3">
-        <v>1200</v>
       </c>
       <c r="O66" s="3">
         <v>1200</v>
@@ -5108,19 +5266,19 @@
         <v>1200</v>
       </c>
       <c r="Q66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R66" s="3">
         <v>1400</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1200</v>
       </c>
       <c r="S66" s="3">
         <v>1200</v>
       </c>
       <c r="T66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U66" s="3">
         <v>1300</v>
-      </c>
-      <c r="U66" s="3">
-        <v>100</v>
       </c>
       <c r="V66" s="3">
         <v>100</v>
@@ -5129,25 +5287,28 @@
         <v>100</v>
       </c>
       <c r="X66" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y66" s="3">
         <v>300</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>100</v>
       </c>
       <c r="Z66" s="3">
         <v>100</v>
       </c>
       <c r="AA66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="3">
         <v>100</v>
       </c>
-      <c r="AC66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5406,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>400</v>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-16300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-9800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-9100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-300</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
       <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="3">
         <v>-100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-900</v>
       </c>
       <c r="G81" s="3">
         <v>-900</v>
       </c>
       <c r="H81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6241,8 +6440,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -6283,17 +6482,20 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>4</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-800</v>
       </c>
       <c r="Q89" s="3">
         <v>-800</v>
       </c>
       <c r="R89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-200</v>
       </c>
       <c r="AA89" s="3">
         <v>-200</v>
       </c>
       <c r="AB89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6853,8 +7074,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,59 +7297,62 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>400</v>
+      </c>
+      <c r="E94" s="3">
         <v>900</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>6800</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -7132,29 +7362,32 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7216,8 +7450,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,47 +7759,50 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>4900</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -7570,26 +7816,26 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>3800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>2100</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,8 +7880,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-4500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>100</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-100</v>
       </c>
       <c r="AA102" s="3">
         <v>-100</v>
       </c>
       <c r="AB102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SILO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>SILO</t>
   </si>
@@ -656,137 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -811,14 +818,14 @@
       <c r="J8" s="3">
         <v>0</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
+      <c r="K8" s="3">
+        <v>0</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -874,8 +881,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -900,14 +913,14 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
@@ -937,14 +950,14 @@
         <v>0</v>
       </c>
       <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
         <v>100</v>
       </c>
-      <c r="X9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>0</v>
-      </c>
       <c r="Z9" s="3">
         <v>0</v>
       </c>
@@ -954,17 +967,23 @@
       <c r="AB9" s="3">
         <v>0</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>4</v>
+      <c r="AC9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -989,14 +1008,14 @@
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
@@ -1026,14 +1045,14 @@
         <v>0</v>
       </c>
       <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
         <v>-100</v>
       </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
       <c r="Z10" s="3">
         <v>0</v>
       </c>
@@ -1043,17 +1062,23 @@
       <c r="AB10" s="3">
         <v>0</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD10" s="3" t="s">
-        <v>4</v>
+      <c r="AC10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,73 +1110,75 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="3">
-        <v>200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N12" s="3">
         <v>200</v>
       </c>
       <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>500</v>
-      </c>
-      <c r="T12" s="3">
-        <v>100</v>
-      </c>
-      <c r="U12" s="3">
-        <v>100</v>
       </c>
       <c r="V12" s="3">
         <v>100</v>
       </c>
       <c r="W12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y12" s="3">
         <v>0</v>
@@ -1160,22 +1187,28 @@
         <v>0</v>
       </c>
       <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3">
         <v>100</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,97 +1296,109 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>4</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>4</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>800</v>
+      </c>
+      <c r="F17" s="3">
         <v>1200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L17" s="3">
-        <v>800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1100</v>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N17" s="3">
         <v>800</v>
       </c>
       <c r="O17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P17" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
-      </c>
-      <c r="R17" s="3">
-        <v>500</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1000</v>
       </c>
       <c r="T17" s="3">
         <v>500</v>
       </c>
       <c r="U17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V17" s="3">
+        <v>500</v>
+      </c>
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>400</v>
       </c>
       <c r="AB17" s="3">
         <v>200</v>
       </c>
       <c r="AC17" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AD17" s="3">
         <v>200</v>
       </c>
       <c r="AE17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1100</v>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N18" s="3">
         <v>-800</v>
       </c>
       <c r="O18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-1000</v>
       </c>
       <c r="T18" s="3">
         <v>-500</v>
       </c>
       <c r="U18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-400</v>
       </c>
       <c r="AB18" s="3">
         <v>-200</v>
       </c>
       <c r="AC18" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="AD18" s="3">
         <v>-200</v>
       </c>
       <c r="AE18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,25 +1747,27 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1708,11 +1775,11 @@
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>4</v>
@@ -1720,36 +1787,36 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
       </c>
       <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V20" s="3">
         <v>7000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1763,82 +1830,88 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-800</v>
-      </c>
       <c r="M21" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
+      <c r="O21" s="3">
+        <v>-1100</v>
       </c>
       <c r="P21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>6500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1857,11 +1930,17 @@
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1886,14 +1965,14 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1901,20 +1980,20 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1929,117 +2008,129 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>6500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2076,11 +2167,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2106,17 +2197,17 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2127,8 +2218,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>6500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>6500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2537,31 +2658,31 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V29" s="3">
         <v>-100</v>
       </c>
       <c r="W29" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="X29" s="3">
         <v>-100</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,25 +2883,31 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2776,11 +2915,11 @@
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>4</v>
@@ -2788,36 +2927,36 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
       </c>
       <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-7000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2831,105 +2970,117 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>6400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>6400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,8 +3437,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3275,73 +3448,73 @@
         <v>3900</v>
       </c>
       <c r="E41" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G41" s="3">
         <v>4300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>11400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>12300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>8700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>9800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>10300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1900</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>100</v>
       </c>
       <c r="AB41" s="3">
         <v>0</v>
@@ -3350,79 +3523,85 @@
         <v>100</v>
       </c>
       <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF41" s="3">
         <v>200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F42" s="3">
         <v>1900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>2300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>3200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>3100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>8600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>6000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>600</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
@@ -3436,21 +3615,27 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AE42" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -3474,10 +3659,10 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
@@ -3485,20 +3670,20 @@
       <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
+      <c r="P43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>100</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3510,22 +3695,22 @@
         <v>0</v>
       </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>100</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>200</v>
       </c>
       <c r="AA43" s="3">
         <v>200</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
+      <c r="AB43" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>200</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>4</v>
@@ -3533,8 +3718,14 @@
       <c r="AE43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3571,11 +3762,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3586,56 +3777,62 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>4</v>
+      <c r="T44" s="3">
+        <v>0</v>
       </c>
       <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W44" s="3">
         <v>100</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
       <c r="X44" s="3">
         <v>0</v>
       </c>
       <c r="Y44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA44" s="3">
         <v>200</v>
       </c>
       <c r="AB44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD44" s="3">
         <v>100</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>0</v>
-      </c>
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
@@ -3661,16 +3858,16 @@
         <v>0</v>
       </c>
       <c r="O45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -3679,7 +3876,7 @@
         <v>200</v>
       </c>
       <c r="U45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>200</v>
@@ -3688,17 +3885,17 @@
         <v>200</v>
       </c>
       <c r="X45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>500</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
       <c r="AB45" s="3">
         <v>0</v>
       </c>
@@ -3711,97 +3908,109 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F46" s="3">
         <v>6200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>7100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>7700</v>
-      </c>
-      <c r="J46" s="3">
-        <v>6900</v>
       </c>
       <c r="K46" s="3">
         <v>7700</v>
       </c>
       <c r="L46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="N46" s="3">
         <v>8900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>10200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>11000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>11600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>8900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>9600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>10400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>11300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>5000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>5500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3838,14 +4047,14 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>100</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3">
         <v>100</v>
@@ -3856,11 +4065,11 @@
       <c r="T47" s="3">
         <v>100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
+      <c r="U47" s="3">
+        <v>100</v>
+      </c>
+      <c r="V47" s="3">
+        <v>100</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>4</v>
@@ -3874,14 +4083,14 @@
       <c r="Z47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>200</v>
+      <c r="AA47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC47" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD47" s="3">
         <v>200</v>
@@ -3889,8 +4098,14 @@
       <c r="AE47" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3927,11 +4142,11 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -3978,8 +4193,14 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4002,10 +4223,10 @@
         <v>200</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -4016,14 +4237,14 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -4067,8 +4288,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,31 +4478,37 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -4283,18 +4522,18 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
@@ -4307,18 +4546,18 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
+      <c r="W52" s="3">
+        <v>0</v>
       </c>
       <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
@@ -4334,8 +4573,14 @@
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,82 +4668,88 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F54" s="3">
         <v>6400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>8000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>7700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>9000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>11000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>11600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>13000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>9000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>9700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>10500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>11400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2800</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>500</v>
       </c>
       <c r="AB54" s="3">
         <v>400</v>
@@ -4507,13 +4758,19 @@
         <v>500</v>
       </c>
       <c r="AD54" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE54" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF54" s="3">
         <v>800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,8 +4837,10 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4587,64 +4848,64 @@
         <v>600</v>
       </c>
       <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
+        <v>600</v>
+      </c>
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>600</v>
       </c>
       <c r="M57" s="3">
         <v>700</v>
       </c>
       <c r="N57" s="3">
+        <v>600</v>
+      </c>
+      <c r="O57" s="3">
+        <v>700</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
       </c>
       <c r="S57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
       </c>
       <c r="U57" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="V57" s="3">
         <v>200</v>
       </c>
       <c r="W57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y57" s="3">
         <v>100</v>
@@ -4659,16 +4920,22 @@
         <v>100</v>
       </c>
       <c r="AC57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4739,25 +5006,31 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>100</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4818,17 +5091,17 @@
       <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
+      <c r="W59" s="3">
+        <v>100</v>
+      </c>
+      <c r="X59" s="3">
+        <v>100</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>4</v>
@@ -4839,14 +5112,20 @@
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
+      <c r="AD59" s="3">
+        <v>0</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4854,79 +5133,79 @@
         <v>700</v>
       </c>
       <c r="E60" s="3">
+        <v>700</v>
+      </c>
+      <c r="F60" s="3">
+        <v>700</v>
+      </c>
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
-      </c>
-      <c r="L60" s="3">
-        <v>700</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1100</v>
       </c>
       <c r="N60" s="3">
         <v>700</v>
       </c>
       <c r="O60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P60" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q60" s="3">
         <v>400</v>
-      </c>
-      <c r="P60" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>300</v>
       </c>
       <c r="R60" s="3">
         <v>300</v>
       </c>
       <c r="S60" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="T60" s="3">
         <v>300</v>
       </c>
       <c r="U60" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="V60" s="3">
         <v>300</v>
       </c>
       <c r="W60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X60" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Y60" s="3">
         <v>100</v>
       </c>
       <c r="Z60" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AA60" s="3">
         <v>100</v>
       </c>
       <c r="AB60" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC60" s="3">
         <v>100</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>0</v>
       </c>
       <c r="AD60" s="3">
         <v>100</v>
@@ -4934,8 +5213,14 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5023,8 +5308,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5061,11 +5352,11 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>900</v>
-      </c>
-      <c r="P62" s="3">
-        <v>900</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>900</v>
@@ -5077,20 +5368,20 @@
         <v>900</v>
       </c>
       <c r="T62" s="3">
+        <v>900</v>
+      </c>
+      <c r="U62" s="3">
+        <v>900</v>
+      </c>
+      <c r="V62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>900</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
@@ -5103,17 +5394,23 @@
       <c r="AB62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,88 +5688,94 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F66" s="3">
         <v>1400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1300</v>
-      </c>
-      <c r="P66" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1200</v>
       </c>
       <c r="R66" s="3">
         <v>1200</v>
       </c>
       <c r="S66" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="T66" s="3">
         <v>1200</v>
       </c>
       <c r="U66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V66" s="3">
         <v>1200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X66" s="3">
         <v>1300</v>
-      </c>
-      <c r="W66" s="3">
-        <v>100</v>
-      </c>
-      <c r="X66" s="3">
-        <v>100</v>
       </c>
       <c r="Y66" s="3">
         <v>100</v>
       </c>
       <c r="Z66" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AA66" s="3">
         <v>100</v>
       </c>
       <c r="AB66" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC66" s="3">
         <v>100</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>0</v>
       </c>
       <c r="AD66" s="3">
         <v>100</v>
@@ -5468,8 +5783,14 @@
       <c r="AE66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5748,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3">
         <v>400</v>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-18600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-17500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-16300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-15300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-13500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-12600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-11700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-10900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-9800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-9100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-8100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-7200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-4500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-3900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-3300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-2200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-8600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-8100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-5800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F76" s="3">
         <v>5000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>10300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>11900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>9100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>10200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-300</v>
       </c>
-      <c r="AA76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="3">
         <v>-100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>6400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +7002,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6645,11 +7042,11 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -6687,17 +7084,23 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,67 +7568,73 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-500</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-300</v>
       </c>
       <c r="W89" s="3">
         <v>-500</v>
@@ -7210,28 +7643,34 @@
         <v>-300</v>
       </c>
       <c r="Y89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7702,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7301,11 +7742,11 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7352,8 +7793,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7983,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>900</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3">
         <v>1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>6800</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7690,11 +8157,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,56 +8493,62 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>600</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
+      <c r="F100" s="3">
+        <v>600</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>4900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -8068,37 +8559,43 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>3800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2100</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>400</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8135,11 +8632,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8186,93 +8683,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-4500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>6100</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-500</v>
-      </c>
-      <c r="V102" s="3">
-        <v>3500</v>
       </c>
       <c r="W102" s="3">
         <v>-500</v>
       </c>
       <c r="X102" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>1900</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>100</v>
       </c>
       <c r="AB102" s="3">
         <v>-100</v>
       </c>
       <c r="AC102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>
